--- a/backend/data/HélioBénin_Prix.xlsx
+++ b/backend/data/HélioBénin_Prix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VICTUS\Desktop\heliobenin\backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VICTUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC0A70A-8DE8-4EDF-941B-DF499DCF7688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6A5C3C-8FC7-410C-8EC4-66651626DB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Protection &amp; Câble" sheetId="1" r:id="rId1"/>
@@ -518,13 +518,32 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF2C3E50"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF2C3E50"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -542,37 +561,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF2C3E50"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF2C3E50"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF2C3E50"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
@@ -766,165 +754,164 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1231,1753 +1218,1753 @@
   <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="35" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12" style="2" customWidth="1"/>
-    <col min="7" max="9" width="8.88671875" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="5" style="17" customWidth="1"/>
+    <col min="2" max="2" width="35" style="17" customWidth="1"/>
+    <col min="3" max="3" width="18" style="17" customWidth="1"/>
+    <col min="4" max="4" width="16" style="17" customWidth="1"/>
+    <col min="5" max="5" width="8" style="17" customWidth="1"/>
+    <col min="6" max="6" width="12" style="17" customWidth="1"/>
+    <col min="7" max="9" width="8.88671875" style="17" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="18">
         <v>1376</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="18">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="18">
         <v>1966</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="18">
         <v>2753</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="18">
         <v>4326</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="18">
         <v>6685</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="A7" s="18">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="20">
         <v>10400</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="A8" s="18">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="20">
         <v>14800</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="A9" s="18">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="22">
         <v>2723</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="18">
+        <v>9</v>
+      </c>
+      <c r="B10" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="22">
         <v>3932</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="A11" s="18">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="22">
         <v>5748</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="A12" s="18">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="22">
         <v>8000</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="A13" s="18">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="22">
         <v>11200</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="A14" s="18">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="22">
         <v>15700</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="A15" s="18">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="22">
         <v>22000</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="A16" s="18">
         <v>15</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="24">
         <v>1936</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+      <c r="A17" s="18">
         <v>16</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="24">
         <v>2662</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+      <c r="A18" s="18">
         <v>17</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="24">
         <v>3730</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
+      <c r="A19" s="18">
         <v>18</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="24">
         <v>5600</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="A20" s="18">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="24">
         <v>8400</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
+      <c r="A21" s="18">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="26">
         <v>2904</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="A22" s="18">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="26">
         <v>4356</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+      <c r="A23" s="18">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="26">
         <v>6100</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="A24" s="18">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="26">
         <v>9150</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+      <c r="A25" s="18">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="26">
         <v>13730</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+      <c r="A26" s="18">
         <v>25</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="E26" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="31">
+      <c r="E26" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="46">
         <v>14500</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+      <c r="A27" s="18">
         <v>26</v>
       </c>
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="33" t="s">
+      <c r="D27" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="E27" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="33">
+      <c r="E27" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="48">
         <v>14859</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+      <c r="A28" s="18">
         <v>27</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="D28" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="33">
+      <c r="E28" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="48">
         <v>15609</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
+      <c r="A29" s="18">
         <v>28</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="D29" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="E29" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="31">
+      <c r="E29" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="46">
         <v>16000</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+      <c r="A30" s="18">
         <v>29</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="33">
+      <c r="E30" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="48">
         <v>17085</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
+      <c r="A31" s="18">
         <v>30</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="33">
+      <c r="E31" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="48">
         <v>19312</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
+      <c r="A32" s="18">
         <v>31</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="D32" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="E32" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="33">
+      <c r="E32" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="48">
         <v>21313</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
+      <c r="A33" s="18">
         <v>32</v>
       </c>
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="E33" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="33">
+      <c r="E33" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="48">
         <v>23643</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
+      <c r="A34" s="18">
         <v>33</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="33" t="s">
+      <c r="D34" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="E34" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="33">
+      <c r="E34" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="48">
         <v>26741</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
+      <c r="A35" s="18">
         <v>34</v>
       </c>
-      <c r="B35" s="32" t="s">
+      <c r="B35" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C35" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D35" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="E35" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="31">
+      <c r="E35" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="46">
         <v>31500</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
+      <c r="A36" s="18">
         <v>35</v>
       </c>
-      <c r="B36" s="32" t="s">
+      <c r="B36" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D36" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="E36" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="31">
+      <c r="E36" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="46">
         <v>37000</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
+      <c r="A37" s="18">
         <v>36</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="13">
+      <c r="E37" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="28">
         <v>6776</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="3">
+      <c r="A38" s="18">
         <v>37</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="13">
+      <c r="E38" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="28">
         <v>6776</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
+      <c r="A39" s="18">
         <v>38</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="13">
+      <c r="E39" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="28">
         <v>6776</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
+      <c r="A40" s="18">
         <v>39</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="13">
+      <c r="E40" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="28">
         <v>7115</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
+      <c r="A41" s="18">
         <v>40</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E41" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="13">
+      <c r="E41" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="28">
         <v>7454</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
+      <c r="A42" s="18">
         <v>41</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="E42" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="13">
+      <c r="E42" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="28">
         <v>7792</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
+      <c r="A43" s="18">
         <v>42</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="E43" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" s="13">
+      <c r="E43" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="28">
         <v>8131</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
+      <c r="A44" s="18">
         <v>43</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="E44" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="13">
+      <c r="E44" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="28">
         <v>8809</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="3">
+      <c r="A45" s="18">
         <v>44</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" s="13">
+      <c r="E45" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="28">
         <v>11000</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="3">
+      <c r="A46" s="18">
         <v>45</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="53">
+        <v>13200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="18">
+        <v>46</v>
+      </c>
+      <c r="B47" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="53">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="18">
+        <v>47</v>
+      </c>
+      <c r="B48" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="26">
+        <v>22603</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="18">
+        <v>48</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="26">
+        <v>23619</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="18">
+        <v>49</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" s="26">
+        <v>26717</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="18">
+        <v>50</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" s="26">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="18">
+        <v>51</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="E46" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" s="37">
-        <v>13200</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3">
-        <v>46</v>
-      </c>
-      <c r="B47" s="12" t="s">
+      <c r="E52" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" s="26">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="18">
+        <v>52</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" s="26">
+        <v>34848</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="18">
+        <v>53</v>
+      </c>
+      <c r="B54" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E54" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="26">
+        <v>39204</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="18">
+        <v>54</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" s="26">
+        <v>43560</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="18">
+        <v>55</v>
+      </c>
+      <c r="B56" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="C56" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="50">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="18">
+        <v>56</v>
+      </c>
+      <c r="B57" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="C57" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="E57" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="50">
+        <v>71000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="18">
+        <v>57</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="30">
+        <v>17970</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="18">
+        <v>58</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="30">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="18">
+        <v>59</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D60" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E60" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="30">
+        <v>29500</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="18">
+        <v>60</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="30">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="18">
+        <v>61</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="E62" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="30">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="18">
+        <v>62</v>
+      </c>
+      <c r="B63" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D63" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="E63" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="30">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="18">
+        <v>63</v>
+      </c>
+      <c r="B64" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E64" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="30">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="18">
+        <v>64</v>
+      </c>
+      <c r="B65" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C65" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D65" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="E65" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="38">
+        <v>6393</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="18">
+        <v>65</v>
+      </c>
+      <c r="B66" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C66" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="E66" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="38">
+        <v>8442</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="18">
+        <v>66</v>
+      </c>
+      <c r="B67" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C67" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D67" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="E67" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" s="38">
+        <v>8442</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="18">
+        <v>67</v>
+      </c>
+      <c r="B68" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C68" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D68" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="E68" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="38">
+        <v>10230</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="18">
+        <v>68</v>
+      </c>
+      <c r="B69" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C69" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D69" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="E69" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="38">
+        <v>11935</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="18">
+        <v>69</v>
+      </c>
+      <c r="B70" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C70" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="E70" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="38">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="18">
+        <v>70</v>
+      </c>
+      <c r="B71" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C71" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D71" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E71" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="40">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="18">
+        <v>71</v>
+      </c>
+      <c r="B72" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C72" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D72" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="E72" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="40">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="18">
+        <v>72</v>
+      </c>
+      <c r="B73" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="D73" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="E73" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="42">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="18">
+        <v>73</v>
+      </c>
+      <c r="B74" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="D74" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="E74" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="42">
+        <v>59583</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="18">
+        <v>74</v>
+      </c>
+      <c r="B75" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C75" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="D75" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="E75" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="42">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="18">
+        <v>75</v>
+      </c>
+      <c r="B76" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="C76" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="D76" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="E76" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" s="42">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="18">
+        <v>76</v>
+      </c>
+      <c r="B77" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D77" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="E77" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="44">
+        <v>108000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="18">
+        <v>77</v>
+      </c>
+      <c r="B78" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C78" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D78" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="E78" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="36">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="18">
         <v>78</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="B79" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C79" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D79" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="36">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="18">
         <v>79</v>
       </c>
-      <c r="D47" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" s="35">
-        <v>21500</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3">
-        <v>47</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" s="11" t="s">
+      <c r="B80" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C80" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="E80" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="33">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="18">
+        <v>80</v>
+      </c>
+      <c r="B81" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C81" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D81" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="E81" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="33">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="18">
+        <v>81</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C82" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D82" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E82" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="33">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="18">
+        <v>82</v>
+      </c>
+      <c r="B83" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C83" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D83" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="E48" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" s="11">
-        <v>22603</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3">
-        <v>48</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D49" s="11" t="s">
+      <c r="E83" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="33">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="18">
+        <v>83</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C84" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D84" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="E84" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="33">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="18">
+        <v>84</v>
+      </c>
+      <c r="B85" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C85" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D85" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="E49" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="11">
-        <v>23619</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
-        <v>49</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" s="11">
-        <v>26717</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
-        <v>50</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="11">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="3">
-        <v>51</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" s="11">
-        <v>44000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="3">
-        <v>52</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" s="11">
-        <v>34848</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="3">
-        <v>53</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" s="11">
-        <v>39204</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3">
-        <v>54</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" s="11">
-        <v>43560</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="3">
-        <v>55</v>
-      </c>
-      <c r="B56" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C56" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D56" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" s="35">
-        <v>56000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="3">
-        <v>56</v>
-      </c>
-      <c r="B57" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C57" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D57" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="E57" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="35">
-        <v>71000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="3">
-        <v>57</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E58" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" s="15">
-        <v>17970</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="3">
-        <v>58</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D59" s="15" t="s">
+      <c r="E85" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="36">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="18">
         <v>85</v>
       </c>
-      <c r="E59" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" s="15">
-        <v>22500</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="3">
-        <v>59</v>
-      </c>
-      <c r="B60" s="16" t="s">
+      <c r="B86" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C86" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="E86" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="36">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="18">
         <v>86</v>
       </c>
-      <c r="C60" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E60" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="15">
-        <v>29500</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="3">
-        <v>60</v>
-      </c>
-      <c r="B61" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E61" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="15">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="3">
-        <v>61</v>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E62" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="15">
-        <v>15500</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="3">
-        <v>62</v>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C63" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E63" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" s="15">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="3">
-        <v>63</v>
-      </c>
-      <c r="B64" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D64" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="15">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="3">
-        <v>64</v>
-      </c>
-      <c r="B65" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C65" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="E65" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="23">
-        <v>6393</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="3">
-        <v>65</v>
-      </c>
-      <c r="B66" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="E66" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="23">
-        <v>8442</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="3">
-        <v>66</v>
-      </c>
-      <c r="B67" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C67" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="E67" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" s="23">
-        <v>8442</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="3">
-        <v>67</v>
-      </c>
-      <c r="B68" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C68" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E68" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="23">
-        <v>10230</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="3">
-        <v>68</v>
-      </c>
-      <c r="B69" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C69" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D69" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="E69" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="23">
-        <v>11935</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="3">
-        <v>69</v>
-      </c>
-      <c r="B70" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C70" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" s="23">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="3">
-        <v>70</v>
-      </c>
-      <c r="B71" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="C71" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D71" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="E71" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="25">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="3">
-        <v>71</v>
-      </c>
-      <c r="B72" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="E72" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="25">
-        <v>23500</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="3">
-        <v>72</v>
-      </c>
-      <c r="B73" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C73" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D73" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E73" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" s="27">
-        <v>55000</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="3">
-        <v>73</v>
-      </c>
-      <c r="B74" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C74" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D74" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="27">
-        <v>59583</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="3">
-        <v>74</v>
-      </c>
-      <c r="B75" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C75" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D75" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="E75" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="27">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="3">
-        <v>75</v>
-      </c>
-      <c r="B76" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="C76" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D76" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="E76" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" s="27">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="3">
-        <v>76</v>
-      </c>
-      <c r="B77" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="C77" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D77" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="E77" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" s="29">
-        <v>108000</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="3">
-        <v>77</v>
-      </c>
-      <c r="B78" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C78" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D78" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E78" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" s="21">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="3">
-        <v>78</v>
-      </c>
-      <c r="B79" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C79" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D79" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="E79" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" s="21">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="3">
-        <v>79</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D80" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E80" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" s="18">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="3">
-        <v>80</v>
-      </c>
-      <c r="B81" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D81" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E81" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F81" s="18">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3">
-        <v>81</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C82" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D82" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="E82" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" s="18">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="3">
-        <v>82</v>
-      </c>
-      <c r="B83" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D83" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" s="18">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3">
-        <v>83</v>
-      </c>
-      <c r="B84" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D84" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E84" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" s="18">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="3">
-        <v>84</v>
-      </c>
-      <c r="B85" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C85" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D85" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E85" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F85" s="21">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="3">
-        <v>85</v>
-      </c>
-      <c r="B86" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C86" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D86" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="E86" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" s="21">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="3">
-        <v>86</v>
-      </c>
-      <c r="B87" s="19" t="s">
+      <c r="B87" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="C87" s="20" t="s">
+      <c r="C87" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="D87" s="20" t="s">
+      <c r="D87" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="E87" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" s="20">
+      <c r="E87" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="35">
         <v>8500</v>
       </c>
     </row>
@@ -2994,492 +2981,491 @@
   <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" style="39" customWidth="1"/>
-    <col min="2" max="2" width="35" style="39" customWidth="1"/>
-    <col min="3" max="3" width="12" style="39" customWidth="1"/>
-    <col min="4" max="4" width="18" style="39" customWidth="1"/>
-    <col min="5" max="5" width="8" style="39" customWidth="1"/>
-    <col min="6" max="6" width="12" style="39" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="39"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="40">
+      <c r="E2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="12">
         <v>157500</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="40">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="40">
+      <c r="E3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="12">
         <v>189000</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="40">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="40">
+      <c r="E4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="12">
         <v>210000</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="40">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="40">
+      <c r="E5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="12">
         <v>231000</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="40">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="40">
+      <c r="E6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="12">
         <v>252000</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
+      <c r="A7" s="14">
         <v>6</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="42">
+      <c r="E7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="14">
         <v>294000</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="42">
+      <c r="A8" s="14">
         <v>7</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="42">
+      <c r="E8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="14">
         <v>367500</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="42">
+      <c r="A9" s="14">
         <v>8</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="42">
+      <c r="E9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="14">
         <v>472500</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="42">
-        <v>9</v>
-      </c>
-      <c r="B10" s="43" t="s">
+      <c r="A10" s="14">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="42">
+      <c r="E10" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="14">
         <v>504000</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="42">
+      <c r="A11" s="14">
         <v>10</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="42">
+      <c r="E11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="14">
         <v>546000</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="44">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="44">
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2">
         <v>567000</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="44">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="44">
+      <c r="E13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2">
         <v>609000</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="44">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="44">
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2">
         <v>619500</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="44">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="44">
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2">
         <v>672000</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="44">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="44">
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2">
         <v>693000</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="44">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="44">
+      <c r="E17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2">
         <v>735000</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="44" t="s">
+      <c r="C18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="44" t="s">
+      <c r="D18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="44">
+      <c r="E18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2">
         <v>756000</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="44">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="D19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="44">
+      <c r="E19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="2">
         <v>787500</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="44">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="44">
+      <c r="E20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="2">
         <v>840000</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="44">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="44" t="s">
+      <c r="D21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="44">
+      <c r="E21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="2">
         <v>861000</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="44">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="44">
+      <c r="E22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2">
         <v>892500</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="44">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="44">
+      <c r="E23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="2">
         <v>1102500</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="44">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E24" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="44">
+      <c r="E24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="2">
         <v>1312500</v>
       </c>
     </row>
@@ -3493,472 +3479,471 @@
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" style="39" customWidth="1"/>
-    <col min="2" max="2" width="35" style="39" customWidth="1"/>
-    <col min="3" max="3" width="14" style="39" customWidth="1"/>
-    <col min="4" max="4" width="18" style="39" customWidth="1"/>
-    <col min="5" max="5" width="8" style="39" customWidth="1"/>
-    <col min="6" max="6" width="14" style="39" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="39"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="46">
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4">
         <v>118125</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="46">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E3" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="46">
+      <c r="E3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4">
         <v>236250</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="46">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E4" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="46">
+      <c r="E4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="4">
         <v>354375</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="46">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="46">
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4">
         <v>472500</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="46">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E6" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="46">
+      <c r="E6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4">
         <v>661500</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="46">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E7" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="46">
+      <c r="E7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="4">
         <v>708750</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="46">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E8" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="46">
+      <c r="E8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="4">
         <v>945000</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="48">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E9" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="48">
+      <c r="E9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6">
         <v>236250</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48">
-        <v>9</v>
-      </c>
-      <c r="B10" s="49" t="s">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E10" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="48">
+      <c r="E10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6">
         <v>472500</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="48">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E11" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="48">
+      <c r="E11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="6">
         <v>708750</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E12" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="48">
+      <c r="E12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="6">
         <v>945000</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E13" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="48">
+      <c r="E13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="6">
         <v>1323000</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="48">
+      <c r="E14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="6">
         <v>1417500</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E15" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="48">
+      <c r="E15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="6">
         <v>1890000</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="50">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E16" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="50">
+      <c r="E16" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="8">
         <v>472500</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="50">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E17" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="50">
+      <c r="E17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="8">
         <v>945000</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="50">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="50" t="s">
+      <c r="D18" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="E18" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="50">
+      <c r="E18" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="8">
         <v>1134000</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="50">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="D19" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E19" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="50">
+      <c r="E19" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="8">
         <v>1417500</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="50">
+      <c r="A20" s="8">
         <v>19</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D20" s="50" t="s">
+      <c r="D20" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E20" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="50">
+      <c r="E20" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="8">
         <v>1890000</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="50">
+      <c r="A21" s="8">
         <v>20</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D21" s="50" t="s">
+      <c r="D21" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="E21" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="50">
+      <c r="E21" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="8">
         <v>2646000</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="50">
+      <c r="A22" s="8">
         <v>21</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="50" t="s">
+      <c r="D22" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="E22" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="50">
+      <c r="E22" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="8">
         <v>2835000</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="50">
+      <c r="A23" s="8">
         <v>22</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D23" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E23" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="50">
+      <c r="E23" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="8">
         <v>3780000</v>
       </c>
     </row>
@@ -3972,72 +3957,71 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" style="39" customWidth="1"/>
-    <col min="2" max="2" width="45" style="39" customWidth="1"/>
-    <col min="3" max="3" width="12" style="39" customWidth="1"/>
-    <col min="4" max="4" width="18" style="39" customWidth="1"/>
-    <col min="5" max="5" width="8" style="39" customWidth="1"/>
-    <col min="6" max="6" width="12" style="39" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="39"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="52" t="s">
         <v>161</v>
       </c>
-      <c r="E2" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="53">
+      <c r="E2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="10">
         <v>55500</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="53">
+      <c r="E3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="10">
         <v>99750</v>
       </c>
     </row>
